--- a/data/trans_orig/P41D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto a la última vez que lo intentaron se quedó embarazada en 2023</t>
+          <t>Población según si con respecto a la última vez que lo intentaron se quedó embarazada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,62 +765,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>697</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -1416,97 +1416,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5092</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>28,69%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>70,8%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2063</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4998</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,69%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6293</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>15,51%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>69,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5812</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Estudios-trans_orig.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
